--- a/Results/LinearRegressionResults_jan262025.xlsx
+++ b/Results/LinearRegressionResults_jan262025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kx2\Documents\kxu\Acoustic-Touchscreen-Attachment-ML\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kev\Documents\kxu\CMU\Year 1\Acoustic-Touchscreen-Attachment-ML\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73A421B-DB2C-4438-8C00-110CDADD58C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703D26D0-21D1-49EB-BEFE-12EBBA9F8E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23284,9 +23284,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X200"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>0.3</v>
       </c>
@@ -23301,7 +23301,7 @@
         <v>0.79150601309135027</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.3</v>
       </c>
@@ -23315,7 +23315,7 @@
         <v>0.69789269057566727</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.3</v>
       </c>
@@ -23329,7 +23329,7 @@
         <v>0.78616087634320664</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.3</v>
       </c>
@@ -23343,7 +23343,7 @@
         <v>0.67939109871823788</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -23357,7 +23357,7 @@
         <v>0.62376472926576909</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0.3</v>
       </c>
@@ -23371,7 +23371,7 @@
         <v>0.51885678946950264</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.3</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>0.66631858964484891</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0.3</v>
       </c>
@@ -23399,7 +23399,7 @@
         <v>0.5804599192392601</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.3</v>
       </c>
@@ -23413,7 +23413,7 @@
         <v>0.42947944215362449</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.3</v>
       </c>
@@ -23427,7 +23427,7 @@
         <v>0.59501400711134877</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0.3</v>
       </c>
@@ -23441,7 +23441,7 @@
         <v>1.057529471809374</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0.3</v>
       </c>
@@ -23455,7 +23455,7 @@
         <v>1.108701827562246</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0.3</v>
       </c>
@@ -23469,7 +23469,7 @@
         <v>1.1019429871399249</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0.3</v>
       </c>
@@ -23483,7 +23483,7 @@
         <v>1.1483291376832729</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0.3</v>
       </c>
@@ -23497,7 +23497,7 @@
         <v>0.89863327677008087</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0.3</v>
       </c>
@@ -23511,7 +23511,7 @@
         <v>1.136202954131075</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0.3</v>
       </c>
@@ -23525,7 +23525,7 @@
         <v>0.69811624010608497</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>0.3</v>
       </c>
@@ -23539,7 +23539,7 @@
         <v>0.80328718391260878</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>0.3</v>
       </c>
@@ -23553,7 +23553,7 @@
         <v>1.074422433762777</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>0.3</v>
       </c>
@@ -23567,7 +23567,7 @@
         <v>1.0284183274475791</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>0.6</v>
       </c>
@@ -23581,7 +23581,7 @@
         <v>0.59978138429177719</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>0.6</v>
       </c>
@@ -23595,7 +23595,7 @@
         <v>-1.1511620892211029E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>0.6</v>
       </c>
@@ -23609,7 +23609,7 @@
         <v>0.20052959876450061</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>0.6</v>
       </c>
@@ -23623,7 +23623,7 @@
         <v>0.17346813165196551</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>0.6</v>
       </c>
@@ -23637,7 +23637,7 @@
         <v>0.180525598588126</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>0.6</v>
       </c>
@@ -23651,7 +23651,7 @@
         <v>0.18719518539162999</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>0.6</v>
       </c>
@@ -23665,7 +23665,7 @@
         <v>0.13096979860704749</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>0.6</v>
       </c>
@@ -23679,7 +23679,7 @@
         <v>0.15454511742889571</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>0.6</v>
       </c>
@@ -23693,7 +23693,7 @@
         <v>0.30976229547496459</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>0.6</v>
       </c>
@@ -23707,7 +23707,7 @@
         <v>5.0203202116609447E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>0.6</v>
       </c>
@@ -23721,7 +23721,7 @@
         <v>0.93273949681154988</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>0.6</v>
       </c>
@@ -23735,7 +23735,7 @@
         <v>0.85234980794420778</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>0.6</v>
       </c>
@@ -23749,7 +23749,7 @@
         <v>1.1017996425586141</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>0.6</v>
       </c>
@@ -23763,7 +23763,7 @@
         <v>1.138378086056903</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>0.6</v>
       </c>
@@ -23777,7 +23777,7 @@
         <v>1.295872863233924</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>0.6</v>
       </c>
@@ -23791,7 +23791,7 @@
         <v>1.186530852392085</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>0.6</v>
       </c>
@@ -23805,7 +23805,7 @@
         <v>1.013031400310894</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>0.6</v>
       </c>
@@ -23819,7 +23819,7 @@
         <v>1.045892473986356</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>0.6</v>
       </c>
@@ -23833,7 +23833,7 @@
         <v>0.7029258698682348</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>0.6</v>
       </c>
@@ -23847,7 +23847,7 @@
         <v>0.78984083263764404</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>0.9</v>
       </c>
@@ -23861,7 +23861,7 @@
         <v>0.95098841498959175</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>0.9</v>
       </c>
@@ -23875,7 +23875,7 @@
         <v>1.0108202085459941</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>0.9</v>
       </c>
@@ -23889,7 +23889,7 @@
         <v>0.68362159946320844</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>0.9</v>
       </c>
@@ -23903,7 +23903,7 @@
         <v>0.7625278568458711</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>0.9</v>
       </c>
@@ -23917,7 +23917,7 @@
         <v>0.8773543961421062</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>0.9</v>
       </c>
@@ -23931,7 +23931,7 @@
         <v>0.80084331733494452</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>0.9</v>
       </c>
@@ -23945,7 +23945,7 @@
         <v>0.92916555858261063</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>0.9</v>
       </c>
@@ -23959,7 +23959,7 @@
         <v>0.58837378703029586</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>0.9</v>
       </c>
@@ -23973,7 +23973,7 @@
         <v>1.038219870725452</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>0.9</v>
       </c>
@@ -23987,7 +23987,7 @@
         <v>0.75004292449701992</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>0.9</v>
       </c>
@@ -24001,7 +24001,7 @@
         <v>1.3106476606510109</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>0.9</v>
       </c>
@@ -24015,7 +24015,7 @@
         <v>0.9906773153830386</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>0.9</v>
       </c>
@@ -24029,7 +24029,7 @@
         <v>1.107656579540631</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>0.9</v>
       </c>
@@ -24043,7 +24043,7 @@
         <v>1.059807984684934</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>0.9</v>
       </c>
@@ -24057,7 +24057,7 @@
         <v>1.150224633203734</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>0.9</v>
       </c>
@@ -24071,7 +24071,7 @@
         <v>1.219947826481921</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>0.9</v>
       </c>
@@ -24085,7 +24085,7 @@
         <v>1.0837033547023469</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>0.9</v>
       </c>
@@ -24099,7 +24099,7 @@
         <v>1.195788847085151</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>0.9</v>
       </c>
@@ -24113,7 +24113,7 @@
         <v>1.1825143895740311</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>0.9</v>
       </c>
@@ -24127,7 +24127,7 @@
         <v>1.152527767302743</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1.2</v>
       </c>
@@ -24141,7 +24141,7 @@
         <v>1.615782601374999</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1.2</v>
       </c>
@@ -24155,7 +24155,7 @@
         <v>1.1165576403817179</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1.2</v>
       </c>
@@ -24169,7 +24169,7 @@
         <v>1.2941173103903689</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1.2</v>
       </c>
@@ -24183,7 +24183,7 @@
         <v>1.080237391250201</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1.2</v>
       </c>
@@ -24197,7 +24197,7 @@
         <v>1.22315439756682</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1.2</v>
       </c>
@@ -24211,7 +24211,7 @@
         <v>1.526982520058382</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1.2</v>
       </c>
@@ -24225,7 +24225,7 @@
         <v>1.236376935901575</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>1.2</v>
       </c>
@@ -24239,7 +24239,7 @@
         <v>1.506861648408353</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>1.2</v>
       </c>
@@ -24253,7 +24253,7 @@
         <v>1.1757570967378901</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>1.2</v>
       </c>
@@ -24267,7 +24267,7 @@
         <v>1.2415374841694169</v>
       </c>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>1.2</v>
       </c>
@@ -24281,7 +24281,7 @@
         <v>1.30752795449806</v>
       </c>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1.2</v>
       </c>
@@ -24295,7 +24295,7 @@
         <v>1.492064255859997</v>
       </c>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>1.2</v>
       </c>
@@ -24309,7 +24309,7 @@
         <v>1.4920241858704979</v>
       </c>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1.2</v>
       </c>
@@ -24323,7 +24323,7 @@
         <v>1.6959116782375749</v>
       </c>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1.2</v>
       </c>
@@ -24337,7 +24337,7 @@
         <v>1.5241938081002111</v>
       </c>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1.2</v>
       </c>
@@ -24351,7 +24351,7 @@
         <v>1.3846610524106211</v>
       </c>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1.2</v>
       </c>
@@ -24365,7 +24365,7 @@
         <v>1.567927566396911</v>
       </c>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1.2</v>
       </c>
@@ -24379,7 +24379,7 @@
         <v>1.62307046555371</v>
       </c>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>1.2</v>
       </c>
@@ -24393,7 +24393,7 @@
         <v>1.640541278780717</v>
       </c>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>1.2</v>
       </c>
@@ -24407,7 +24407,7 @@
         <v>1.7936293697716901</v>
       </c>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>1.5</v>
       </c>
@@ -24421,7 +24421,7 @@
         <v>1.375367179398165</v>
       </c>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>1.5</v>
       </c>
@@ -24435,7 +24435,7 @@
         <v>1.076378566773734</v>
       </c>
     </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1.5</v>
       </c>
@@ -24449,7 +24449,7 @@
         <v>1.1208458635539811</v>
       </c>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1.5</v>
       </c>
@@ -24463,7 +24463,7 @@
         <v>1.115554344740612</v>
       </c>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1.5</v>
       </c>
@@ -24477,7 +24477,7 @@
         <v>0.92189858644283973</v>
       </c>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1.5</v>
       </c>
@@ -24491,7 +24491,7 @@
         <v>1.181728143028089</v>
       </c>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1.5</v>
       </c>
@@ -24505,7 +24505,7 @@
         <v>0.98887309263700729</v>
       </c>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1.5</v>
       </c>
@@ -24519,7 +24519,7 @@
         <v>0.88411599837981569</v>
       </c>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1.5</v>
       </c>
@@ -24533,7 +24533,7 @@
         <v>1.269507138835223</v>
       </c>
     </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1.5</v>
       </c>
@@ -24547,7 +24547,7 @@
         <v>1.2679851487137379</v>
       </c>
     </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>1.5</v>
       </c>
@@ -24561,7 +24561,7 @@
         <v>1.4823857470923021</v>
       </c>
     </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1.5</v>
       </c>
@@ -24575,7 +24575,7 @@
         <v>1.669510186561322</v>
       </c>
     </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1.5</v>
       </c>
@@ -24589,7 +24589,7 @@
         <v>1.234121617435491</v>
       </c>
     </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1.5</v>
       </c>
@@ -24603,7 +24603,7 @@
         <v>1.48872273036741</v>
       </c>
     </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1.5</v>
       </c>
@@ -24617,7 +24617,7 @@
         <v>1.595020732013555</v>
       </c>
     </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1.5</v>
       </c>
@@ -24631,7 +24631,7 @@
         <v>1.4423940524205681</v>
       </c>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>1.5</v>
       </c>
@@ -24645,7 +24645,7 @@
         <v>1.6700869015027671</v>
       </c>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1.5</v>
       </c>
@@ -24659,7 +24659,7 @@
         <v>1.624148553785794</v>
       </c>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1.5</v>
       </c>
@@ -24673,7 +24673,7 @@
         <v>1.498227596581202</v>
       </c>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>1.5</v>
       </c>
@@ -24687,7 +24687,7 @@
         <v>1.407261232769873</v>
       </c>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1.8</v>
       </c>
@@ -24701,7 +24701,7 @@
         <v>1.41963956941321</v>
       </c>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1.8</v>
       </c>
@@ -24715,7 +24715,7 @@
         <v>1.419749158825425</v>
       </c>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1.8</v>
       </c>
@@ -24729,7 +24729,7 @@
         <v>1.4062010564862819</v>
       </c>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1.8</v>
       </c>
@@ -24743,7 +24743,7 @@
         <v>1.8382891418610221</v>
       </c>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1.8</v>
       </c>
@@ -24757,7 +24757,7 @@
         <v>1.5271289539923321</v>
       </c>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>1.8</v>
       </c>
@@ -24771,7 +24771,7 @@
         <v>1.429900595040259</v>
       </c>
     </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>1.8</v>
       </c>
@@ -24785,7 +24785,7 @@
         <v>1.0770649084410979</v>
       </c>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>1.8</v>
       </c>
@@ -24799,7 +24799,7 @@
         <v>1.5999370261732899</v>
       </c>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>1.8</v>
       </c>
@@ -24813,7 +24813,7 @@
         <v>1.4718374330706081</v>
       </c>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1.8</v>
       </c>
@@ -24827,7 +24827,7 @@
         <v>1.3576554466052679</v>
       </c>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>1.8</v>
       </c>
@@ -24841,7 +24841,7 @@
         <v>1.287080299857557</v>
       </c>
     </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1.8</v>
       </c>
@@ -24855,7 +24855,7 @@
         <v>1.605865750892598</v>
       </c>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>1.8</v>
       </c>
@@ -24869,7 +24869,7 @@
         <v>1.362432211184281</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1.8</v>
       </c>
@@ -24883,7 +24883,7 @@
         <v>1.768008962246171</v>
       </c>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>1.8</v>
       </c>
@@ -24897,7 +24897,7 @@
         <v>1.766504297608716</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>1.8</v>
       </c>
@@ -24911,7 +24911,7 @@
         <v>1.4243613810475679</v>
       </c>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1.8</v>
       </c>
@@ -24925,7 +24925,7 @@
         <v>1.286279174808403</v>
       </c>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>1.8</v>
       </c>
@@ -24939,7 +24939,7 @@
         <v>2.0372585326872499</v>
       </c>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1.8</v>
       </c>
@@ -24953,7 +24953,7 @@
         <v>1.605287974220907</v>
       </c>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>1.8</v>
       </c>
@@ -24967,7 +24967,7 @@
         <v>1.4615526153957601</v>
       </c>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2.1</v>
       </c>
@@ -24981,7 +24981,7 @@
         <v>1.841479040450142</v>
       </c>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2.1</v>
       </c>
@@ -24995,7 +24995,7 @@
         <v>2.2591890443883642</v>
       </c>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2.1</v>
       </c>
@@ -25009,7 +25009,7 @@
         <v>1.855477668560731</v>
       </c>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2.1</v>
       </c>
@@ -25023,7 +25023,7 @@
         <v>1.924330774586803</v>
       </c>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2.1</v>
       </c>
@@ -25037,7 +25037,7 @@
         <v>2.058940129450495</v>
       </c>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2.1</v>
       </c>
@@ -25051,7 +25051,7 @@
         <v>2.2159444387015981</v>
       </c>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2.1</v>
       </c>
@@ -25065,7 +25065,7 @@
         <v>2.0475905539790382</v>
       </c>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2.1</v>
       </c>
@@ -25079,7 +25079,7 @@
         <v>2.2044414753873589</v>
       </c>
     </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2.1</v>
       </c>
@@ -25093,7 +25093,7 @@
         <v>1.9512075779251501</v>
       </c>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2.1</v>
       </c>
@@ -25107,7 +25107,7 @@
         <v>2.0838222151638282</v>
       </c>
     </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2.1</v>
       </c>
@@ -25121,7 +25121,7 @@
         <v>1.9581130501676469</v>
       </c>
     </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2.1</v>
       </c>
@@ -25135,7 +25135,7 @@
         <v>2.406773056818889</v>
       </c>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2.1</v>
       </c>
@@ -25149,7 +25149,7 @@
         <v>2.193023091797798</v>
       </c>
     </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2.1</v>
       </c>
@@ -25163,7 +25163,7 @@
         <v>2.174123980245668</v>
       </c>
     </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2.1</v>
       </c>
@@ -25177,7 +25177,7 @@
         <v>2.3945028109180271</v>
       </c>
     </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2.1</v>
       </c>
@@ -25191,7 +25191,7 @@
         <v>2.6076823883383109</v>
       </c>
     </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2.1</v>
       </c>
@@ -25205,7 +25205,7 @@
         <v>1.9094399201103021</v>
       </c>
     </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2.1</v>
       </c>
@@ -25219,7 +25219,7 @@
         <v>2.0806867941145062</v>
       </c>
     </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2.1</v>
       </c>
@@ -25233,7 +25233,7 @@
         <v>2.2465578710419578</v>
       </c>
     </row>
-    <row r="140" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2.1</v>
       </c>
@@ -25247,7 +25247,7 @@
         <v>1.964930248511457</v>
       </c>
     </row>
-    <row r="141" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2.4</v>
       </c>
@@ -25261,7 +25261,7 @@
         <v>2.7282774073865959</v>
       </c>
     </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2.4</v>
       </c>
@@ -25275,7 +25275,7 @@
         <v>2.3407836853056661</v>
       </c>
     </row>
-    <row r="143" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2.4</v>
       </c>
@@ -25289,7 +25289,7 @@
         <v>2.9843127490957322</v>
       </c>
     </row>
-    <row r="144" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2.4</v>
       </c>
@@ -25303,7 +25303,7 @@
         <v>2.724797025221406</v>
       </c>
     </row>
-    <row r="145" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2.4</v>
       </c>
@@ -25317,7 +25317,7 @@
         <v>2.6936604246485309</v>
       </c>
     </row>
-    <row r="146" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2.4</v>
       </c>
@@ -25331,7 +25331,7 @@
         <v>2.8217540037894189</v>
       </c>
     </row>
-    <row r="147" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2.4</v>
       </c>
@@ -25345,7 +25345,7 @@
         <v>2.7903034912847922</v>
       </c>
     </row>
-    <row r="148" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2.4</v>
       </c>
@@ -25359,7 +25359,7 @@
         <v>2.779826763116414</v>
       </c>
     </row>
-    <row r="149" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2.4</v>
       </c>
@@ -25373,7 +25373,7 @@
         <v>2.6021650651475952</v>
       </c>
     </row>
-    <row r="150" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2.4</v>
       </c>
@@ -25387,7 +25387,7 @@
         <v>2.67621538833717</v>
       </c>
     </row>
-    <row r="151" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2.4</v>
       </c>
@@ -25401,7 +25401,7 @@
         <v>2.676461841669223</v>
       </c>
     </row>
-    <row r="152" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2.4</v>
       </c>
@@ -25415,7 +25415,7 @@
         <v>2.4664402757853132</v>
       </c>
     </row>
-    <row r="153" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2.4</v>
       </c>
@@ -25429,7 +25429,7 @@
         <v>3.0199837598404322</v>
       </c>
     </row>
-    <row r="154" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2.4</v>
       </c>
@@ -25443,7 +25443,7 @@
         <v>2.7629088363091761</v>
       </c>
     </row>
-    <row r="155" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2.4</v>
       </c>
@@ -25457,7 +25457,7 @@
         <v>2.6073335523317742</v>
       </c>
     </row>
-    <row r="156" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2.4</v>
       </c>
@@ -25471,7 +25471,7 @@
         <v>2.6623119829482391</v>
       </c>
     </row>
-    <row r="157" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2.4</v>
       </c>
@@ -25485,7 +25485,7 @@
         <v>2.8440223000233722</v>
       </c>
     </row>
-    <row r="158" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2.4</v>
       </c>
@@ -25499,7 +25499,7 @@
         <v>2.8021314692698809</v>
       </c>
     </row>
-    <row r="159" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2.4</v>
       </c>
@@ -25513,7 +25513,7 @@
         <v>2.8929123697907362</v>
       </c>
     </row>
-    <row r="160" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2.4</v>
       </c>
@@ -25527,7 +25527,7 @@
         <v>2.586423883365228</v>
       </c>
     </row>
-    <row r="161" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2.7</v>
       </c>
@@ -25541,7 +25541,7 @@
         <v>2.549331558291652</v>
       </c>
     </row>
-    <row r="162" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2.7</v>
       </c>
@@ -25555,7 +25555,7 @@
         <v>3.071134617464939</v>
       </c>
     </row>
-    <row r="163" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2.7</v>
       </c>
@@ -25569,7 +25569,7 @@
         <v>3.0418559603016528</v>
       </c>
     </row>
-    <row r="164" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2.7</v>
       </c>
@@ -25583,7 +25583,7 @@
         <v>3.0399283574876041</v>
       </c>
     </row>
-    <row r="165" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2.7</v>
       </c>
@@ -25597,7 +25597,7 @@
         <v>2.7597589697028622</v>
       </c>
     </row>
-    <row r="166" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2.7</v>
       </c>
@@ -25611,7 +25611,7 @@
         <v>2.802560574378592</v>
       </c>
     </row>
-    <row r="167" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2.7</v>
       </c>
@@ -25625,7 +25625,7 @@
         <v>2.9265273195778039</v>
       </c>
     </row>
-    <row r="168" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2.7</v>
       </c>
@@ -25639,7 +25639,7 @@
         <v>2.7935730981296172</v>
       </c>
     </row>
-    <row r="169" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2.7</v>
       </c>
@@ -25653,7 +25653,7 @@
         <v>2.6506177906543802</v>
       </c>
     </row>
-    <row r="170" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2.7</v>
       </c>
@@ -25667,7 +25667,7 @@
         <v>3.1288372853608339</v>
       </c>
     </row>
-    <row r="171" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2.7</v>
       </c>
@@ -25681,7 +25681,7 @@
         <v>2.4540534914368699</v>
       </c>
     </row>
-    <row r="172" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2.7</v>
       </c>
@@ -25695,7 +25695,7 @@
         <v>2.2853531496222139</v>
       </c>
     </row>
-    <row r="173" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2.7</v>
       </c>
@@ -25709,7 +25709,7 @@
         <v>2.4118962686896421</v>
       </c>
     </row>
-    <row r="174" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2.7</v>
       </c>
@@ -25723,7 +25723,7 @@
         <v>2.4521363664428582</v>
       </c>
     </row>
-    <row r="175" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2.7</v>
       </c>
@@ -25737,7 +25737,7 @@
         <v>2.4181131506189222</v>
       </c>
     </row>
-    <row r="176" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2.7</v>
       </c>
@@ -25751,7 +25751,7 @@
         <v>2.3363850371926418</v>
       </c>
     </row>
-    <row r="177" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2.7</v>
       </c>
@@ -25765,7 +25765,7 @@
         <v>2.5925538517157669</v>
       </c>
     </row>
-    <row r="178" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2.7</v>
       </c>
@@ -25779,7 +25779,7 @@
         <v>2.4344335265316239</v>
       </c>
     </row>
-    <row r="179" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2.7</v>
       </c>
@@ -25793,7 +25793,7 @@
         <v>2.4685868973185978</v>
       </c>
     </row>
-    <row r="180" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2.7</v>
       </c>
@@ -25807,7 +25807,7 @@
         <v>2.1833808699577131</v>
       </c>
     </row>
-    <row r="181" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>3</v>
       </c>
@@ -25821,7 +25821,7 @@
         <v>2.6178440696395242</v>
       </c>
     </row>
-    <row r="182" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>3</v>
       </c>
@@ -25835,7 +25835,7 @@
         <v>2.5869242999683379</v>
       </c>
     </row>
-    <row r="183" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>3</v>
       </c>
@@ -25849,7 +25849,7 @@
         <v>2.9029106756176968</v>
       </c>
     </row>
-    <row r="184" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>3</v>
       </c>
@@ -25863,7 +25863,7 @@
         <v>2.6639536751443491</v>
       </c>
     </row>
-    <row r="185" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>3</v>
       </c>
@@ -25877,7 +25877,7 @@
         <v>2.6593879449617219</v>
       </c>
     </row>
-    <row r="186" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>3</v>
       </c>
@@ -25891,7 +25891,7 @@
         <v>2.5900386497855439</v>
       </c>
     </row>
-    <row r="187" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>3</v>
       </c>
@@ -25905,7 +25905,7 @@
         <v>2.0746816362931848</v>
       </c>
     </row>
-    <row r="188" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>3</v>
       </c>
@@ -25919,7 +25919,7 @@
         <v>2.7362950884263171</v>
       </c>
     </row>
-    <row r="189" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>3</v>
       </c>
@@ -25933,7 +25933,7 @@
         <v>2.6189491377148069</v>
       </c>
     </row>
-    <row r="190" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>3</v>
       </c>
@@ -25947,7 +25947,7 @@
         <v>2.845463410278239</v>
       </c>
     </row>
-    <row r="191" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>3</v>
       </c>
@@ -25961,7 +25961,7 @@
         <v>2.705149689900153</v>
       </c>
     </row>
-    <row r="192" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>3</v>
       </c>
@@ -25975,7 +25975,7 @@
         <v>2.8650038714483341</v>
       </c>
     </row>
-    <row r="193" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>3</v>
       </c>
@@ -25989,7 +25989,7 @@
         <v>2.90882099396983</v>
       </c>
     </row>
-    <row r="194" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>3</v>
       </c>
@@ -26003,7 +26003,7 @@
         <v>2.8273890972780289</v>
       </c>
     </row>
-    <row r="195" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>3</v>
       </c>
@@ -26017,7 +26017,7 @@
         <v>2.599414617554018</v>
       </c>
     </row>
-    <row r="196" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>3</v>
       </c>
@@ -26031,7 +26031,7 @@
         <v>2.445360807806896</v>
       </c>
     </row>
-    <row r="197" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>3</v>
       </c>
@@ -26045,7 +26045,7 @@
         <v>2.622871238230605</v>
       </c>
     </row>
-    <row r="198" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>3</v>
       </c>
@@ -26059,7 +26059,7 @@
         <v>2.8231288886229109</v>
       </c>
     </row>
-    <row r="199" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>3</v>
       </c>
@@ -26073,7 +26073,7 @@
         <v>2.5855119821045069</v>
       </c>
     </row>
-    <row r="200" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>3</v>
       </c>
@@ -26096,9 +26096,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A54795E-42BC-48B7-A82F-77488CA505CF}">
   <dimension ref="A1:S200"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>0.3</v>
       </c>
@@ -26112,7 +26112,7 @@
         <v>0.22244760296702279</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.3</v>
       </c>
@@ -26126,7 +26126,7 @@
         <v>0.25791384129154687</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.3</v>
       </c>
@@ -26140,7 +26140,7 @@
         <v>0.24407635217563239</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.3</v>
       </c>
@@ -26154,7 +26154,7 @@
         <v>0.23593310668224629</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -26168,7 +26168,7 @@
         <v>0.25791069984458659</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0.3</v>
       </c>
@@ -26182,7 +26182,7 @@
         <v>0.2468042495012952</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.3</v>
       </c>
@@ -26196,7 +26196,7 @@
         <v>0.24424766487258151</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0.3</v>
       </c>
@@ -26210,7 +26210,7 @@
         <v>0.23681365164428311</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.3</v>
       </c>
@@ -26224,7 +26224,7 @@
         <v>0.19867884170307801</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.3</v>
       </c>
@@ -26238,7 +26238,7 @@
         <v>0.21928302405222411</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0.3</v>
       </c>
@@ -26252,7 +26252,7 @@
         <v>0.33908705856941879</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0.3</v>
       </c>
@@ -26266,7 +26266,7 @@
         <v>0.31460446214272508</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0.3</v>
       </c>
@@ -26280,7 +26280,7 @@
         <v>0.33971340680970741</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0.3</v>
       </c>
@@ -26294,7 +26294,7 @@
         <v>0.30750386584718831</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0.3</v>
       </c>
@@ -26308,7 +26308,7 @@
         <v>0.40838876712179939</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0.3</v>
       </c>
@@ -26322,7 +26322,7 @@
         <v>0.2785595957265059</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0.3</v>
       </c>
@@ -26336,7 +26336,7 @@
         <v>0.34073098559072429</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>0.3</v>
       </c>
@@ -26350,7 +26350,7 @@
         <v>0.33541875839312502</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>0.3</v>
       </c>
@@ -26364,7 +26364,7 @@
         <v>0.38713730172022309</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>0.3</v>
       </c>
@@ -26378,7 +26378,7 @@
         <v>0.37109334386846632</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>0.6</v>
       </c>
@@ -26392,7 +26392,7 @@
         <v>0.89413420654348386</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>0.6</v>
       </c>
@@ -26406,7 +26406,7 @@
         <v>0.85937740649349337</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>0.6</v>
       </c>
@@ -26420,7 +26420,7 @@
         <v>0.84052144282991037</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>0.6</v>
       </c>
@@ -26434,7 +26434,7 @@
         <v>0.88455974790966962</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>0.6</v>
       </c>
@@ -26448,7 +26448,7 @@
         <v>0.86253457232479036</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>0.6</v>
       </c>
@@ -26462,7 +26462,7 @@
         <v>0.9096154529297138</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>0.6</v>
       </c>
@@ -26476,7 +26476,7 @@
         <v>0.936843778255394</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>0.6</v>
       </c>
@@ -26490,7 +26490,7 @@
         <v>0.87109478206831881</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>0.6</v>
       </c>
@@ -26504,7 +26504,7 @@
         <v>0.91173960619414629</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>0.6</v>
       </c>
@@ -26518,7 +26518,7 @@
         <v>0.88840874056916164</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>0.6</v>
       </c>
@@ -26532,7 +26532,7 @@
         <v>0.71506435111849953</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>0.6</v>
       </c>
@@ -26546,7 +26546,7 @@
         <v>0.77917410501694917</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>0.6</v>
       </c>
@@ -26560,7 +26560,7 @@
         <v>0.78466379820854115</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>0.6</v>
       </c>
@@ -26574,7 +26574,7 @@
         <v>0.83801829887371326</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>0.6</v>
       </c>
@@ -26588,7 +26588,7 @@
         <v>0.78810074650069595</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>0.6</v>
       </c>
@@ -26602,7 +26602,7 @@
         <v>0.81213062560162541</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>0.6</v>
       </c>
@@ -26616,7 +26616,7 @@
         <v>0.78553969641087917</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>0.6</v>
       </c>
@@ -26630,7 +26630,7 @@
         <v>1.0197289796863129</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>0.6</v>
       </c>
@@ -26644,7 +26644,7 @@
         <v>0.8082695284891841</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>0.6</v>
       </c>
@@ -26658,7 +26658,7 @@
         <v>1.0147327412152261</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>0.9</v>
       </c>
@@ -26672,7 +26672,7 @@
         <v>0.97420018907848061</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>0.9</v>
       </c>
@@ -26686,7 +26686,7 @@
         <v>0.95530014090215332</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>0.9</v>
       </c>
@@ -26700,7 +26700,7 @@
         <v>0.83625699517409657</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>0.9</v>
       </c>
@@ -26714,7 +26714,7 @@
         <v>0.94195834579507931</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>0.9</v>
       </c>
@@ -26728,7 +26728,7 @@
         <v>0.9427896181782387</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>0.9</v>
       </c>
@@ -26742,7 +26742,7 @@
         <v>0.94526890964147015</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>0.9</v>
       </c>
@@ -26756,7 +26756,7 @@
         <v>0.91102696054847598</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>0.9</v>
       </c>
@@ -26770,7 +26770,7 @@
         <v>0.93588458778003769</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>0.9</v>
       </c>
@@ -26784,7 +26784,7 @@
         <v>0.94264658974010729</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>0.9</v>
       </c>
@@ -26798,7 +26798,7 @@
         <v>0.9340568769536759</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>0.9</v>
       </c>
@@ -26812,7 +26812,7 @@
         <v>0.95706618425869294</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>0.9</v>
       </c>
@@ -26826,7 +26826,7 @@
         <v>0.95889652276187576</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>0.9</v>
       </c>
@@ -26840,7 +26840,7 @@
         <v>0.87956204694865647</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>0.9</v>
       </c>
@@ -26854,7 +26854,7 @@
         <v>0.75600259312249563</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>0.9</v>
       </c>
@@ -26868,7 +26868,7 @@
         <v>0.87375066038443805</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>0.9</v>
       </c>
@@ -26882,7 +26882,7 @@
         <v>0.85256339863477137</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>0.9</v>
       </c>
@@ -26896,7 +26896,7 @@
         <v>0.83678917615343806</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>0.9</v>
       </c>
@@ -26910,7 +26910,7 @@
         <v>0.89703465069127475</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>0.9</v>
       </c>
@@ -26924,7 +26924,7 @@
         <v>0.90363365127415562</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>0.9</v>
       </c>
@@ -26938,7 +26938,7 @@
         <v>0.89366850255417063</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1.2</v>
       </c>
@@ -26952,7 +26952,7 @@
         <v>1.267670110703925</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1.2</v>
       </c>
@@ -26966,7 +26966,7 @@
         <v>1.1569659341747709</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1.2</v>
       </c>
@@ -26980,7 +26980,7 @@
         <v>1.214807731886701</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1.2</v>
       </c>
@@ -26994,7 +26994,7 @@
         <v>1.1612487753316501</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1.2</v>
       </c>
@@ -27008,7 +27008,7 @@
         <v>1.1975966867362471</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1.2</v>
       </c>
@@ -27022,7 +27022,7 @@
         <v>1.182202533253204</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1.2</v>
       </c>
@@ -27036,7 +27036,7 @@
         <v>1.1948345273955849</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>1.2</v>
       </c>
@@ -27050,7 +27050,7 @@
         <v>1.186204116063649</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>1.2</v>
       </c>
@@ -27064,7 +27064,7 @@
         <v>1.1366137271040131</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>1.2</v>
       </c>
@@ -27078,7 +27078,7 @@
         <v>1.1590262022996569</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>1.2</v>
       </c>
@@ -27092,7 +27092,7 @@
         <v>1.22843529771685</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1.2</v>
       </c>
@@ -27106,7 +27106,7 @@
         <v>1.15990749929172</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>1.2</v>
       </c>
@@ -27120,7 +27120,7 @@
         <v>1.197049326281906</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1.2</v>
       </c>
@@ -27134,7 +27134,7 @@
         <v>1.2070836838799861</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1.2</v>
       </c>
@@ -27148,7 +27148,7 @@
         <v>1.1975455628702749</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1.2</v>
       </c>
@@ -27162,7 +27162,7 @@
         <v>1.2366235532509291</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1.2</v>
       </c>
@@ -27176,7 +27176,7 @@
         <v>1.2025495069112819</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1.2</v>
       </c>
@@ -27190,7 +27190,7 @@
         <v>1.2447806933821399</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>1.2</v>
       </c>
@@ -27204,7 +27204,7 @@
         <v>1.2433333635082779</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>1.2</v>
       </c>
@@ -27218,7 +27218,7 @@
         <v>1.232704896919167</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>1.5</v>
       </c>
@@ -27232,7 +27232,7 @@
         <v>1.5386359690989979</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>1.5</v>
       </c>
@@ -27246,7 +27246,7 @@
         <v>1.505909874799698</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1.5</v>
       </c>
@@ -27260,7 +27260,7 @@
         <v>1.5197657473034309</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1.5</v>
       </c>
@@ -27274,7 +27274,7 @@
         <v>1.545129429376018</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1.5</v>
       </c>
@@ -27288,7 +27288,7 @@
         <v>1.5353230576019139</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1.5</v>
       </c>
@@ -27302,7 +27302,7 @@
         <v>1.5431755144010919</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1.5</v>
       </c>
@@ -27316,7 +27316,7 @@
         <v>1.5368688142621489</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1.5</v>
       </c>
@@ -27330,7 +27330,7 @@
         <v>1.5013237208316921</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1.5</v>
       </c>
@@ -27344,7 +27344,7 @@
         <v>1.44998079642945</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1.5</v>
       </c>
@@ -27358,7 +27358,7 @@
         <v>1.52934037251066</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>1.5</v>
       </c>
@@ -27372,7 +27372,7 @@
         <v>1.4944013684356681</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1.5</v>
       </c>
@@ -27386,7 +27386,7 @@
         <v>1.5335753259002229</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1.5</v>
       </c>
@@ -27400,7 +27400,7 @@
         <v>1.512079209720177</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1.5</v>
       </c>
@@ -27414,7 +27414,7 @@
         <v>1.5226451507735701</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1.5</v>
       </c>
@@ -27428,7 +27428,7 @@
         <v>1.5309101945442689</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1.5</v>
       </c>
@@ -27442,7 +27442,7 @@
         <v>1.525670009304569</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>1.5</v>
       </c>
@@ -27456,7 +27456,7 @@
         <v>1.5188485774243929</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1.5</v>
       </c>
@@ -27470,7 +27470,7 @@
         <v>1.5842730867417669</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1.5</v>
       </c>
@@ -27484,7 +27484,7 @@
         <v>1.5284081844926549</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>1.5</v>
       </c>
@@ -27498,7 +27498,7 @@
         <v>1.5296479506121019</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1.8</v>
       </c>
@@ -27512,7 +27512,7 @@
         <v>1.800303519317012</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1.8</v>
       </c>
@@ -27526,7 +27526,7 @@
         <v>1.7723429065831771</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1.8</v>
       </c>
@@ -27540,7 +27540,7 @@
         <v>1.782200400136283</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1.8</v>
       </c>
@@ -27554,7 +27554,7 @@
         <v>1.8571928858818789</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1.8</v>
       </c>
@@ -27568,7 +27568,7 @@
         <v>1.741780919983299</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>1.8</v>
       </c>
@@ -27582,7 +27582,7 @@
         <v>1.7470411954391949</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>1.8</v>
       </c>
@@ -27596,7 +27596,7 @@
         <v>1.796263240798375</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>1.8</v>
       </c>
@@ -27610,7 +27610,7 @@
         <v>1.7562851767410019</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>1.8</v>
       </c>
@@ -27624,7 +27624,7 @@
         <v>1.7502837294400211</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1.8</v>
       </c>
@@ -27638,7 +27638,7 @@
         <v>1.7704178095174681</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>1.8</v>
       </c>
@@ -27652,7 +27652,7 @@
         <v>1.8003099731925969</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1.8</v>
       </c>
@@ -27666,7 +27666,7 @@
         <v>1.8588166922919951</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>1.8</v>
       </c>
@@ -27680,7 +27680,7 @@
         <v>1.825683850373558</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1.8</v>
       </c>
@@ -27694,7 +27694,7 @@
         <v>1.86287329237615</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>1.8</v>
       </c>
@@ -27708,7 +27708,7 @@
         <v>1.8726534556366301</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>1.8</v>
       </c>
@@ -27722,7 +27722,7 @@
         <v>1.8522917202460429</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1.8</v>
       </c>
@@ -27736,7 +27736,7 @@
         <v>1.9143287932519679</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>1.8</v>
       </c>
@@ -27750,7 +27750,7 @@
         <v>1.8947789923130141</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1.8</v>
       </c>
@@ -27764,7 +27764,7 @@
         <v>1.897453981570671</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>1.8</v>
       </c>
@@ -27778,7 +27778,7 @@
         <v>1.7926193851480789</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2.1</v>
       </c>
@@ -27792,7 +27792,7 @@
         <v>2.079343562681863</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2.1</v>
       </c>
@@ -27806,7 +27806,7 @@
         <v>2.125534596483007</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2.1</v>
       </c>
@@ -27820,7 +27820,7 @@
         <v>2.092318899380103</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2.1</v>
       </c>
@@ -27834,7 +27834,7 @@
         <v>2.1472644775140282</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2.1</v>
       </c>
@@ -27848,7 +27848,7 @@
         <v>2.1820634742599481</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2.1</v>
       </c>
@@ -27862,7 +27862,7 @@
         <v>2.0589694141311701</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2.1</v>
       </c>
@@ -27876,7 +27876,7 @@
         <v>2.1940392388706229</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2.1</v>
       </c>
@@ -27890,7 +27890,7 @@
         <v>2.1617973665242118</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2.1</v>
       </c>
@@ -27904,7 +27904,7 @@
         <v>2.1375278436138672</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2.1</v>
       </c>
@@ -27918,7 +27918,7 @@
         <v>2.1341004906316172</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2.1</v>
       </c>
@@ -27932,7 +27932,7 @@
         <v>2.2054157586128942</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2.1</v>
       </c>
@@ -27946,7 +27946,7 @@
         <v>2.173347194564506</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2.1</v>
       </c>
@@ -27960,7 +27960,7 @@
         <v>2.2409491451106192</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2.1</v>
       </c>
@@ -27974,7 +27974,7 @@
         <v>2.3214099505128161</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2.1</v>
       </c>
@@ -27988,7 +27988,7 @@
         <v>2.2084838420504771</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2.1</v>
       </c>
@@ -28002,7 +28002,7 @@
         <v>2.226228216320266</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2.1</v>
       </c>
@@ -28016,7 +28016,7 @@
         <v>2.3362584593876221</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2.1</v>
       </c>
@@ -28030,7 +28030,7 @@
         <v>2.2056609244272352</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2.1</v>
       </c>
@@ -28044,7 +28044,7 @@
         <v>2.2226062981917001</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2.1</v>
       </c>
@@ -28058,7 +28058,7 @@
         <v>2.263198919741392</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2.4</v>
       </c>
@@ -28072,7 +28072,7 @@
         <v>2.2907928942825539</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2.4</v>
       </c>
@@ -28086,7 +28086,7 @@
         <v>2.37322786851604</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2.4</v>
       </c>
@@ -28100,7 +28100,7 @@
         <v>2.2458515030649271</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2.4</v>
       </c>
@@ -28114,7 +28114,7 @@
         <v>2.225233393228343</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2.4</v>
       </c>
@@ -28128,7 +28128,7 @@
         <v>2.324856704978536</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2.4</v>
       </c>
@@ -28142,7 +28142,7 @@
         <v>2.2603098308494012</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2.4</v>
       </c>
@@ -28156,7 +28156,7 @@
         <v>2.2942713090595821</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2.4</v>
       </c>
@@ -28170,7 +28170,7 @@
         <v>2.338858808955806</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2.4</v>
       </c>
@@ -28184,7 +28184,7 @@
         <v>2.2776689129642591</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2.4</v>
       </c>
@@ -28198,7 +28198,7 @@
         <v>2.395250220975143</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2.4</v>
       </c>
@@ -28212,7 +28212,7 @@
         <v>2.373096974472801</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2.4</v>
       </c>
@@ -28226,7 +28226,7 @@
         <v>2.3212493953844979</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2.4</v>
       </c>
@@ -28240,7 +28240,7 @@
         <v>2.3232389412244392</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2.4</v>
       </c>
@@ -28254,7 +28254,7 @@
         <v>2.4130219399900028</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2.4</v>
       </c>
@@ -28268,7 +28268,7 @@
         <v>2.373014203182962</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2.4</v>
       </c>
@@ -28282,7 +28282,7 @@
         <v>2.3866133081365528</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2.4</v>
       </c>
@@ -28296,7 +28296,7 @@
         <v>2.28850764482825</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2.4</v>
       </c>
@@ -28310,7 +28310,7 @@
         <v>2.337782936955954</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2.4</v>
       </c>
@@ -28324,7 +28324,7 @@
         <v>2.371850540196931</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2.4</v>
       </c>
@@ -28338,7 +28338,7 @@
         <v>2.3137854499751431</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2.7</v>
       </c>
@@ -28352,7 +28352,7 @@
         <v>2.951577540563775</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2.7</v>
       </c>
@@ -28366,7 +28366,7 @@
         <v>2.876319749243351</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2.7</v>
       </c>
@@ -28380,7 +28380,7 @@
         <v>2.870359436605177</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2.7</v>
       </c>
@@ -28394,7 +28394,7 @@
         <v>2.9496876499289471</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2.7</v>
       </c>
@@ -28408,7 +28408,7 @@
         <v>2.899382479849685</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2.7</v>
       </c>
@@ -28422,7 +28422,7 @@
         <v>2.8620709979055969</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2.7</v>
       </c>
@@ -28436,7 +28436,7 @@
         <v>2.906387001345685</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2.7</v>
       </c>
@@ -28450,7 +28450,7 @@
         <v>2.9568821181119418</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2.7</v>
       </c>
@@ -28464,7 +28464,7 @@
         <v>2.851835365890302</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2.7</v>
       </c>
@@ -28478,7 +28478,7 @@
         <v>2.789835913356185</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2.7</v>
       </c>
@@ -28492,7 +28492,7 @@
         <v>2.676576127584688</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2.7</v>
       </c>
@@ -28506,7 +28506,7 @@
         <v>2.687574012688962</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2.7</v>
       </c>
@@ -28520,7 +28520,7 @@
         <v>2.7465235852441769</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2.7</v>
       </c>
@@ -28534,7 +28534,7 @@
         <v>2.6711142558998091</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2.7</v>
       </c>
@@ -28548,7 +28548,7 @@
         <v>2.7297405088551732</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2.7</v>
       </c>
@@ -28562,7 +28562,7 @@
         <v>2.724538159968517</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2.7</v>
       </c>
@@ -28576,7 +28576,7 @@
         <v>2.7418833213570011</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2.7</v>
       </c>
@@ -28590,7 +28590,7 @@
         <v>2.7529789438057999</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2.7</v>
       </c>
@@ -28604,7 +28604,7 @@
         <v>2.7361640411171488</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2.7</v>
       </c>
@@ -28618,7 +28618,7 @@
         <v>2.7177539183060588</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>3</v>
       </c>
@@ -28632,7 +28632,7 @@
         <v>2.9471365575704951</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>3</v>
       </c>
@@ -28646,7 +28646,7 @@
         <v>2.997751176470743</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>3</v>
       </c>
@@ -28660,7 +28660,7 @@
         <v>2.989905320451967</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>3</v>
       </c>
@@ -28674,7 +28674,7 @@
         <v>2.9415697325085119</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>3</v>
       </c>
@@ -28688,7 +28688,7 @@
         <v>2.982812375327526</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>3</v>
       </c>
@@ -28702,7 +28702,7 @@
         <v>2.96065862493937</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>3</v>
       </c>
@@ -28716,7 +28716,7 @@
         <v>3.078862418719766</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>3</v>
       </c>
@@ -28730,7 +28730,7 @@
         <v>3.0013126972120081</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>3</v>
       </c>
@@ -28744,7 +28744,7 @@
         <v>3.0212156547655198</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>3</v>
       </c>
@@ -28758,7 +28758,7 @@
         <v>3.030995173953166</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>3</v>
       </c>
@@ -28772,7 +28772,7 @@
         <v>2.8316790412088082</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>3</v>
       </c>
@@ -28786,7 +28786,7 @@
         <v>2.8815397638098972</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>3</v>
       </c>
@@ -28800,7 +28800,7 @@
         <v>2.8947041256400681</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>3</v>
       </c>
@@ -28814,7 +28814,7 @@
         <v>2.7224773204490091</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>3</v>
       </c>
@@ -28828,7 +28828,7 @@
         <v>2.901408808267433</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>3</v>
       </c>
@@ -28842,7 +28842,7 @@
         <v>2.646428931655358</v>
       </c>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>3</v>
       </c>
@@ -28856,7 +28856,7 @@
         <v>2.7184255289978481</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>3</v>
       </c>
@@ -28870,7 +28870,7 @@
         <v>2.7627458385139358</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>3</v>
       </c>
@@ -28884,7 +28884,7 @@
         <v>2.8750376514143809</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>3</v>
       </c>
@@ -28907,9 +28907,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6F2897-9352-452C-948D-3871CB3DFAEC}">
   <dimension ref="A1:AN200"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>0.3</v>
       </c>
@@ -28929,7 +28929,7 @@
         <v>0.28290045928627411</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.3</v>
       </c>
@@ -28949,7 +28949,7 @@
         <v>0.36135336029966442</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.3</v>
       </c>
@@ -28969,7 +28969,7 @@
         <v>0.30460030650500469</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.3</v>
       </c>
@@ -28989,7 +28989,7 @@
         <v>0.33476191773407221</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -29009,7 +29009,7 @@
         <v>0.38520362037217382</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0.3</v>
       </c>
@@ -29029,7 +29029,7 @@
         <v>0.30233718012528338</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.3</v>
       </c>
@@ -29049,7 +29049,7 @@
         <v>0.30491141859175702</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0.3</v>
       </c>
@@ -29069,7 +29069,7 @@
         <v>0.29202018514108619</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.3</v>
       </c>
@@ -29089,7 +29089,7 @@
         <v>0.32643779261260791</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.3</v>
       </c>
@@ -29109,7 +29109,7 @@
         <v>0.29568171401836718</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0.3</v>
       </c>
@@ -29129,7 +29129,7 @@
         <v>0.18690415163542881</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0.3</v>
       </c>
@@ -29149,7 +29149,7 @@
         <v>0.2052449635833595</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0.3</v>
       </c>
@@ -29169,7 +29169,7 @@
         <v>0.19873264003751051</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0.3</v>
       </c>
@@ -29189,7 +29189,7 @@
         <v>0.18789512252900839</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0.3</v>
       </c>
@@ -29209,7 +29209,7 @@
         <v>0.18748418729069921</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0.3</v>
       </c>
@@ -29229,7 +29229,7 @@
         <v>0.16211045166362231</v>
       </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0.3</v>
       </c>
@@ -29249,7 +29249,7 @@
         <v>0.17181336472387221</v>
       </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>0.3</v>
       </c>
@@ -29269,7 +29269,7 @@
         <v>0.19036959767173789</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>0.3</v>
       </c>
@@ -29289,7 +29289,7 @@
         <v>0.1771585528013335</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>0.3</v>
       </c>
@@ -29309,7 +29309,7 @@
         <v>0.16727456313949449</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>0.6</v>
       </c>
@@ -29329,7 +29329,7 @@
         <v>0.5685814589286895</v>
       </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>0.6</v>
       </c>
@@ -29349,7 +29349,7 @@
         <v>0.53048675547601221</v>
       </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>0.6</v>
       </c>
@@ -29369,7 +29369,7 @@
         <v>0.53828804563252741</v>
       </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>0.6</v>
       </c>
@@ -29389,7 +29389,7 @@
         <v>0.55301039978815325</v>
       </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>0.6</v>
       </c>
@@ -29409,7 +29409,7 @@
         <v>0.56032761234257289</v>
       </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>0.6</v>
       </c>
@@ -29429,7 +29429,7 @@
         <v>0.57057028253620889</v>
       </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>0.6</v>
       </c>
@@ -29449,7 +29449,7 @@
         <v>0.49098733511222398</v>
       </c>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>0.6</v>
       </c>
@@ -29469,7 +29469,7 @@
         <v>0.54480428913018497</v>
       </c>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>0.6</v>
       </c>
@@ -29489,7 +29489,7 @@
         <v>0.56641763373800869</v>
       </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>0.6</v>
       </c>
@@ -29509,7 +29509,7 @@
         <v>0.56138832674783012</v>
       </c>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>0.6</v>
       </c>
@@ -29529,7 +29529,7 @@
         <v>0.60388532783827142</v>
       </c>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>0.6</v>
       </c>
@@ -29549,7 +29549,7 @@
         <v>0.62289715945244328</v>
       </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>0.6</v>
       </c>
@@ -29569,7 +29569,7 @@
         <v>0.61015329269316076</v>
       </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>0.6</v>
       </c>
@@ -29589,7 +29589,7 @@
         <v>0.60949596918704896</v>
       </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>0.6</v>
       </c>
@@ -29609,7 +29609,7 @@
         <v>0.59961949881592203</v>
       </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>0.6</v>
       </c>
@@ -29629,7 +29629,7 @@
         <v>0.59624569839041097</v>
       </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>0.6</v>
       </c>
@@ -29649,7 +29649,7 @@
         <v>0.6144274761848374</v>
       </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>0.6</v>
       </c>
@@ -29669,7 +29669,7 @@
         <v>0.61412373253059416</v>
       </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>0.6</v>
       </c>
@@ -29689,7 +29689,7 @@
         <v>0.6186840656933259</v>
       </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>0.6</v>
       </c>
@@ -29709,7 +29709,7 @@
         <v>0.59113221682683426</v>
       </c>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>0.9</v>
       </c>
@@ -29729,7 +29729,7 @@
         <v>1.084388202139291</v>
       </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>0.9</v>
       </c>
@@ -29749,7 +29749,7 @@
         <v>1.066594357455674</v>
       </c>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>0.9</v>
       </c>
@@ -29769,7 +29769,7 @@
         <v>1.0679518667520991</v>
       </c>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>0.9</v>
       </c>
@@ -29789,7 +29789,7 @@
         <v>1.110594532027535</v>
       </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>0.9</v>
       </c>
@@ -29809,7 +29809,7 @@
         <v>1.1312782365604459</v>
       </c>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>0.9</v>
       </c>
@@ -29829,7 +29829,7 @@
         <v>1.094846053724821</v>
       </c>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>0.9</v>
       </c>
@@ -29849,7 +29849,7 @@
         <v>1.0851445132236459</v>
       </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>0.9</v>
       </c>
@@ -29869,7 +29869,7 @@
         <v>1.1108356885818149</v>
       </c>
     </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>0.9</v>
       </c>
@@ -29889,7 +29889,7 @@
         <v>1.103018283568006</v>
       </c>
     </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>0.9</v>
       </c>
@@ -29909,7 +29909,7 @@
         <v>1.121751444214963</v>
       </c>
     </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>0.9</v>
       </c>
@@ -29929,7 +29929,7 @@
         <v>0.84840430130604472</v>
       </c>
     </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>0.9</v>
       </c>
@@ -29949,7 +29949,7 @@
         <v>0.89528806011799889</v>
       </c>
     </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>0.9</v>
       </c>
@@ -29969,7 +29969,7 @@
         <v>0.89457566730946447</v>
       </c>
     </row>
-    <row r="54" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>0.9</v>
       </c>
@@ -29989,7 +29989,7 @@
         <v>0.92360197201745065</v>
       </c>
     </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>0.9</v>
       </c>
@@ -30009,7 +30009,7 @@
         <v>0.90081366071778546</v>
       </c>
     </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>0.9</v>
       </c>
@@ -30029,7 +30029,7 @@
         <v>0.89874201319929004</v>
       </c>
     </row>
-    <row r="57" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>0.9</v>
       </c>
@@ -30049,7 +30049,7 @@
         <v>0.83399575186104991</v>
       </c>
     </row>
-    <row r="58" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>0.9</v>
       </c>
@@ -30069,7 +30069,7 @@
         <v>0.87340820299159105</v>
       </c>
     </row>
-    <row r="59" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>0.9</v>
       </c>
@@ -30089,7 +30089,7 @@
         <v>0.87073781840982667</v>
       </c>
     </row>
-    <row r="60" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>0.9</v>
       </c>
@@ -30109,7 +30109,7 @@
         <v>0.8778488649491123</v>
       </c>
     </row>
-    <row r="61" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1.2</v>
       </c>
@@ -30129,7 +30129,7 @@
         <v>1.219069169304273</v>
       </c>
     </row>
-    <row r="62" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1.2</v>
       </c>
@@ -30149,7 +30149,7 @@
         <v>1.2122487300958671</v>
       </c>
     </row>
-    <row r="63" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1.2</v>
       </c>
@@ -30169,7 +30169,7 @@
         <v>1.226536260851941</v>
       </c>
     </row>
-    <row r="64" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1.2</v>
       </c>
@@ -30189,7 +30189,7 @@
         <v>1.1938947566095739</v>
       </c>
     </row>
-    <row r="65" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1.2</v>
       </c>
@@ -30209,7 +30209,7 @@
         <v>1.210256225595675</v>
       </c>
     </row>
-    <row r="66" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1.2</v>
       </c>
@@ -30229,7 +30229,7 @@
         <v>1.203873215365423</v>
       </c>
     </row>
-    <row r="67" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1.2</v>
       </c>
@@ -30249,7 +30249,7 @@
         <v>1.19889876575209</v>
       </c>
     </row>
-    <row r="68" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>1.2</v>
       </c>
@@ -30269,7 +30269,7 @@
         <v>1.1943371573363379</v>
       </c>
     </row>
-    <row r="69" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>1.2</v>
       </c>
@@ -30289,7 +30289,7 @@
         <v>1.2099726867462619</v>
       </c>
     </row>
-    <row r="70" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>1.2</v>
       </c>
@@ -30309,7 +30309,7 @@
         <v>1.1950770395558381</v>
       </c>
     </row>
-    <row r="71" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>1.2</v>
       </c>
@@ -30329,7 +30329,7 @@
         <v>1.084298135870458</v>
       </c>
     </row>
-    <row r="72" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1.2</v>
       </c>
@@ -30349,7 +30349,7 @@
         <v>1.089103640193311</v>
       </c>
     </row>
-    <row r="73" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>1.2</v>
       </c>
@@ -30369,7 +30369,7 @@
         <v>1.0931547623202009</v>
       </c>
     </row>
-    <row r="74" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1.2</v>
       </c>
@@ -30389,7 +30389,7 @@
         <v>1.1227080100007949</v>
       </c>
     </row>
-    <row r="75" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1.2</v>
       </c>
@@ -30409,7 +30409,7 @@
         <v>1.0954316125305401</v>
       </c>
     </row>
-    <row r="76" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1.2</v>
       </c>
@@ -30429,7 +30429,7 @@
         <v>1.088434680609961</v>
       </c>
     </row>
-    <row r="77" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1.2</v>
       </c>
@@ -30449,7 +30449,7 @@
         <v>1.0635882931667839</v>
       </c>
     </row>
-    <row r="78" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1.2</v>
       </c>
@@ -30469,7 +30469,7 @@
         <v>1.0879266728454</v>
       </c>
     </row>
-    <row r="79" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>1.2</v>
       </c>
@@ -30489,7 +30489,7 @@
         <v>1.0979321711198571</v>
       </c>
     </row>
-    <row r="80" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>1.2</v>
       </c>
@@ -30509,7 +30509,7 @@
         <v>1.087241564771162</v>
       </c>
     </row>
-    <row r="81" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>1.5</v>
       </c>
@@ -30529,7 +30529,7 @@
         <v>1.450790297232571</v>
       </c>
     </row>
-    <row r="82" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>1.5</v>
       </c>
@@ -30549,7 +30549,7 @@
         <v>1.438857647419526</v>
       </c>
     </row>
-    <row r="83" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1.5</v>
       </c>
@@ -30569,7 +30569,7 @@
         <v>1.451366269152494</v>
       </c>
     </row>
-    <row r="84" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1.5</v>
       </c>
@@ -30589,7 +30589,7 @@
         <v>1.4413116652635469</v>
       </c>
     </row>
-    <row r="85" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1.5</v>
       </c>
@@ -30609,7 +30609,7 @@
         <v>1.4323250845362301</v>
       </c>
     </row>
-    <row r="86" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1.5</v>
       </c>
@@ -30629,7 +30629,7 @@
         <v>1.4053329412018929</v>
       </c>
     </row>
-    <row r="87" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1.5</v>
       </c>
@@ -30649,7 +30649,7 @@
         <v>1.4329601009508719</v>
       </c>
     </row>
-    <row r="88" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1.5</v>
       </c>
@@ -30669,7 +30669,7 @@
         <v>1.4240648529942981</v>
       </c>
     </row>
-    <row r="89" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1.5</v>
       </c>
@@ -30689,7 +30689,7 @@
         <v>1.4305741576236071</v>
       </c>
     </row>
-    <row r="90" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1.5</v>
       </c>
@@ -30709,7 +30709,7 @@
         <v>1.4149207740318439</v>
       </c>
     </row>
-    <row r="91" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>1.5</v>
       </c>
@@ -30729,7 +30729,7 @@
         <v>1.2937590123663689</v>
       </c>
     </row>
-    <row r="92" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1.5</v>
       </c>
@@ -30749,7 +30749,7 @@
         <v>1.2908229309838331</v>
       </c>
     </row>
-    <row r="93" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1.5</v>
       </c>
@@ -30769,7 +30769,7 @@
         <v>1.314789788532732</v>
       </c>
     </row>
-    <row r="94" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1.5</v>
       </c>
@@ -30789,7 +30789,7 @@
         <v>1.3730345727442581</v>
       </c>
     </row>
-    <row r="95" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1.5</v>
       </c>
@@ -30809,7 +30809,7 @@
         <v>1.3690193137815689</v>
       </c>
     </row>
-    <row r="96" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1.5</v>
       </c>
@@ -30829,7 +30829,7 @@
         <v>1.3694299353492749</v>
       </c>
     </row>
-    <row r="97" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>1.5</v>
       </c>
@@ -30849,7 +30849,7 @@
         <v>1.403956882854358</v>
       </c>
     </row>
-    <row r="98" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1.5</v>
       </c>
@@ -30869,7 +30869,7 @@
         <v>1.43337266094271</v>
       </c>
     </row>
-    <row r="99" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1.5</v>
       </c>
@@ -30889,7 +30889,7 @@
         <v>1.404220759751132</v>
       </c>
     </row>
-    <row r="100" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>1.5</v>
       </c>
@@ -30909,7 +30909,7 @@
         <v>1.4075772611949171</v>
       </c>
     </row>
-    <row r="101" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1.8</v>
       </c>
@@ -30929,7 +30929,7 @@
         <v>1.848757531776611</v>
       </c>
     </row>
-    <row r="102" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1.8</v>
       </c>
@@ -30949,7 +30949,7 @@
         <v>1.8911024230681159</v>
       </c>
     </row>
-    <row r="103" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1.8</v>
       </c>
@@ -30969,7 +30969,7 @@
         <v>1.890873858609512</v>
       </c>
     </row>
-    <row r="104" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1.8</v>
       </c>
@@ -30989,7 +30989,7 @@
         <v>1.903485939323788</v>
       </c>
     </row>
-    <row r="105" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1.8</v>
       </c>
@@ -31009,7 +31009,7 @@
         <v>1.8656287480771161</v>
       </c>
     </row>
-    <row r="106" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>1.8</v>
       </c>
@@ -31029,7 +31029,7 @@
         <v>1.8328287167713551</v>
       </c>
     </row>
-    <row r="107" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>1.8</v>
       </c>
@@ -31049,7 +31049,7 @@
         <v>1.860728682094037</v>
       </c>
     </row>
-    <row r="108" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>1.8</v>
       </c>
@@ -31069,7 +31069,7 @@
         <v>1.8409340289887881</v>
       </c>
     </row>
-    <row r="109" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>1.8</v>
       </c>
@@ -31089,7 +31089,7 @@
         <v>1.8675309019452919</v>
       </c>
     </row>
-    <row r="110" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1.8</v>
       </c>
@@ -31109,7 +31109,7 @@
         <v>1.8249292731941431</v>
       </c>
     </row>
-    <row r="111" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>1.8</v>
       </c>
@@ -31129,7 +31129,7 @@
         <v>1.990260811992369</v>
       </c>
     </row>
-    <row r="112" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1.8</v>
       </c>
@@ -31149,7 +31149,7 @@
         <v>1.9412902103254419</v>
       </c>
     </row>
-    <row r="113" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>1.8</v>
       </c>
@@ -31169,7 +31169,7 @@
         <v>1.9660950749674471</v>
       </c>
     </row>
-    <row r="114" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1.8</v>
       </c>
@@ -31189,7 +31189,7 @@
         <v>2.0245026266254631</v>
       </c>
     </row>
-    <row r="115" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>1.8</v>
       </c>
@@ -31209,7 +31209,7 @@
         <v>1.9819877099084069</v>
       </c>
     </row>
-    <row r="116" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>1.8</v>
       </c>
@@ -31229,7 +31229,7 @@
         <v>1.9295936383031089</v>
       </c>
     </row>
-    <row r="117" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1.8</v>
       </c>
@@ -31249,7 +31249,7 @@
         <v>1.9523132234308811</v>
       </c>
     </row>
-    <row r="118" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>1.8</v>
       </c>
@@ -31269,7 +31269,7 @@
         <v>1.9867448178530149</v>
       </c>
     </row>
-    <row r="119" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1.8</v>
       </c>
@@ -31289,7 +31289,7 @@
         <v>2.001143270080624</v>
       </c>
     </row>
-    <row r="120" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>1.8</v>
       </c>
@@ -31309,7 +31309,7 @@
         <v>2.0523773941904162</v>
       </c>
     </row>
-    <row r="121" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2.1</v>
       </c>
@@ -31329,7 +31329,7 @@
         <v>2.135407173279436</v>
       </c>
     </row>
-    <row r="122" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2.1</v>
       </c>
@@ -31349,7 +31349,7 @@
         <v>2.097284796967628</v>
       </c>
     </row>
-    <row r="123" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2.1</v>
       </c>
@@ -31369,7 +31369,7 @@
         <v>2.1586380300673378</v>
       </c>
     </row>
-    <row r="124" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2.1</v>
       </c>
@@ -31389,7 +31389,7 @@
         <v>2.121343037938455</v>
       </c>
     </row>
-    <row r="125" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2.1</v>
       </c>
@@ -31409,7 +31409,7 @@
         <v>2.1502894393543861</v>
       </c>
     </row>
-    <row r="126" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2.1</v>
       </c>
@@ -31429,7 +31429,7 @@
         <v>2.1539059457013421</v>
       </c>
     </row>
-    <row r="127" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2.1</v>
       </c>
@@ -31449,7 +31449,7 @@
         <v>2.1057336131430131</v>
       </c>
     </row>
-    <row r="128" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2.1</v>
       </c>
@@ -31469,7 +31469,7 @@
         <v>2.0341113062717588</v>
       </c>
     </row>
-    <row r="129" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2.1</v>
       </c>
@@ -31489,7 +31489,7 @@
         <v>2.137888660143068</v>
       </c>
     </row>
-    <row r="130" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2.1</v>
       </c>
@@ -31509,7 +31509,7 @@
         <v>2.1535315688720251</v>
       </c>
     </row>
-    <row r="131" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2.1</v>
       </c>
@@ -31529,7 +31529,7 @@
         <v>2.1785975692283568</v>
       </c>
     </row>
-    <row r="132" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2.1</v>
       </c>
@@ -31549,7 +31549,7 @@
         <v>2.3040708807432488</v>
       </c>
     </row>
-    <row r="133" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2.1</v>
       </c>
@@ -31569,7 +31569,7 @@
         <v>2.3254877794258149</v>
       </c>
     </row>
-    <row r="134" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2.1</v>
       </c>
@@ -31589,7 +31589,7 @@
         <v>2.2738684095571462</v>
       </c>
     </row>
-    <row r="135" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2.1</v>
       </c>
@@ -31609,7 +31609,7 @@
         <v>2.405700234419494</v>
       </c>
     </row>
-    <row r="136" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2.1</v>
       </c>
@@ -31629,7 +31629,7 @@
         <v>2.3857325646865211</v>
       </c>
     </row>
-    <row r="137" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2.1</v>
       </c>
@@ -31649,7 +31649,7 @@
         <v>2.233186994102129</v>
       </c>
     </row>
-    <row r="138" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2.1</v>
       </c>
@@ -31669,7 +31669,7 @@
         <v>2.3609689805992011</v>
       </c>
     </row>
-    <row r="139" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2.1</v>
       </c>
@@ -31689,7 +31689,7 @@
         <v>2.1320739328181419</v>
       </c>
     </row>
-    <row r="140" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2.1</v>
       </c>
@@ -31709,7 +31709,7 @@
         <v>2.1770211860259492</v>
       </c>
     </row>
-    <row r="141" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2.4</v>
       </c>
@@ -31729,7 +31729,7 @@
         <v>2.3941251019089149</v>
       </c>
     </row>
-    <row r="142" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2.4</v>
       </c>
@@ -31749,7 +31749,7 @@
         <v>2.422108750650767</v>
       </c>
     </row>
-    <row r="143" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2.4</v>
       </c>
@@ -31769,7 +31769,7 @@
         <v>2.3960625832099969</v>
       </c>
     </row>
-    <row r="144" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2.4</v>
       </c>
@@ -31789,7 +31789,7 @@
         <v>2.403417593136175</v>
       </c>
     </row>
-    <row r="145" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2.4</v>
       </c>
@@ -31809,7 +31809,7 @@
         <v>2.375313016398982</v>
       </c>
     </row>
-    <row r="146" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2.4</v>
       </c>
@@ -31829,7 +31829,7 @@
         <v>2.4283457736839109</v>
       </c>
     </row>
-    <row r="147" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2.4</v>
       </c>
@@ -31849,7 +31849,7 @@
         <v>2.4544889172011191</v>
       </c>
     </row>
-    <row r="148" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2.4</v>
       </c>
@@ -31869,7 +31869,7 @@
         <v>2.4196765982212312</v>
       </c>
     </row>
-    <row r="149" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2.4</v>
       </c>
@@ -31889,7 +31889,7 @@
         <v>2.4090832290197581</v>
       </c>
     </row>
-    <row r="150" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2.4</v>
       </c>
@@ -31909,7 +31909,7 @@
         <v>2.4362848055645951</v>
       </c>
     </row>
-    <row r="151" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2.4</v>
       </c>
@@ -31929,7 +31929,7 @@
         <v>2.5598723536176862</v>
       </c>
     </row>
-    <row r="152" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2.4</v>
       </c>
@@ -31949,7 +31949,7 @@
         <v>2.467588523602279</v>
       </c>
     </row>
-    <row r="153" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2.4</v>
       </c>
@@ -31969,7 +31969,7 @@
         <v>2.5060124045581169</v>
       </c>
     </row>
-    <row r="154" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2.4</v>
       </c>
@@ -31989,7 +31989,7 @@
         <v>2.4941267908587159</v>
       </c>
     </row>
-    <row r="155" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2.4</v>
       </c>
@@ -32009,7 +32009,7 @@
         <v>2.4953498357484749</v>
       </c>
     </row>
-    <row r="156" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2.4</v>
       </c>
@@ -32029,7 +32029,7 @@
         <v>2.469262247400795</v>
       </c>
     </row>
-    <row r="157" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2.4</v>
       </c>
@@ -32049,7 +32049,7 @@
         <v>2.46357734864262</v>
       </c>
     </row>
-    <row r="158" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2.4</v>
       </c>
@@ -32069,7 +32069,7 @@
         <v>2.5354845225157101</v>
       </c>
     </row>
-    <row r="159" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2.4</v>
       </c>
@@ -32089,7 +32089,7 @@
         <v>2.5044383252559008</v>
       </c>
     </row>
-    <row r="160" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2.4</v>
       </c>
@@ -32109,7 +32109,7 @@
         <v>2.505566608692726</v>
       </c>
     </row>
-    <row r="161" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2.7</v>
       </c>
@@ -32129,7 +32129,7 @@
         <v>2.5066043063604782</v>
       </c>
     </row>
-    <row r="162" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2.7</v>
       </c>
@@ -32149,7 +32149,7 @@
         <v>2.4773246485144198</v>
       </c>
     </row>
-    <row r="163" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2.7</v>
       </c>
@@ -32169,7 +32169,7 @@
         <v>2.5090654154950398</v>
       </c>
     </row>
-    <row r="164" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2.7</v>
       </c>
@@ -32189,7 +32189,7 @@
         <v>2.5149558795276201</v>
       </c>
     </row>
-    <row r="165" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2.7</v>
       </c>
@@ -32209,7 +32209,7 @@
         <v>2.473628885373897</v>
       </c>
     </row>
-    <row r="166" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2.7</v>
       </c>
@@ -32229,7 +32229,7 @@
         <v>2.4827296025363599</v>
       </c>
     </row>
-    <row r="167" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2.7</v>
       </c>
@@ -32249,7 +32249,7 @@
         <v>2.5377582582486129</v>
       </c>
     </row>
-    <row r="168" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2.7</v>
       </c>
@@ -32269,7 +32269,7 @@
         <v>2.5106704366404951</v>
       </c>
     </row>
-    <row r="169" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2.7</v>
       </c>
@@ -32289,7 +32289,7 @@
         <v>2.516818713145319</v>
       </c>
     </row>
-    <row r="170" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2.7</v>
       </c>
@@ -32309,7 +32309,7 @@
         <v>2.5210437502961209</v>
       </c>
     </row>
-    <row r="171" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2.7</v>
       </c>
@@ -32329,7 +32329,7 @@
         <v>2.469829999328347</v>
       </c>
     </row>
-    <row r="172" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2.7</v>
       </c>
@@ -32349,7 +32349,7 @@
         <v>2.4902598328418901</v>
       </c>
     </row>
-    <row r="173" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2.7</v>
       </c>
@@ -32369,7 +32369,7 @@
         <v>2.4599564444581739</v>
       </c>
     </row>
-    <row r="174" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2.7</v>
       </c>
@@ -32389,7 +32389,7 @@
         <v>2.4373856028627312</v>
       </c>
     </row>
-    <row r="175" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2.7</v>
       </c>
@@ -32409,7 +32409,7 @@
         <v>2.4416936052080982</v>
       </c>
     </row>
-    <row r="176" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2.7</v>
       </c>
@@ -32429,7 +32429,7 @@
         <v>2.4376671569888329</v>
       </c>
     </row>
-    <row r="177" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2.7</v>
       </c>
@@ -32449,7 +32449,7 @@
         <v>2.4109892500600609</v>
       </c>
     </row>
-    <row r="178" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2.7</v>
       </c>
@@ -32469,7 +32469,7 @@
         <v>2.4534639224712871</v>
       </c>
     </row>
-    <row r="179" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2.7</v>
       </c>
@@ -32489,7 +32489,7 @@
         <v>2.4165130244077191</v>
       </c>
     </row>
-    <row r="180" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2.7</v>
       </c>
@@ -32509,7 +32509,7 @@
         <v>2.417014544482011</v>
       </c>
     </row>
-    <row r="181" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>3</v>
       </c>
@@ -32529,7 +32529,7 @@
         <v>3.0713723285278172</v>
       </c>
     </row>
-    <row r="182" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>3</v>
       </c>
@@ -32549,7 +32549,7 @@
         <v>3.1169336457140462</v>
       </c>
     </row>
-    <row r="183" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>3</v>
       </c>
@@ -32569,7 +32569,7 @@
         <v>3.1185136001366738</v>
       </c>
     </row>
-    <row r="184" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>3</v>
       </c>
@@ -32589,7 +32589,7 @@
         <v>3.1346030343117071</v>
       </c>
     </row>
-    <row r="185" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>3</v>
       </c>
@@ -32609,7 +32609,7 @@
         <v>3.143522137490145</v>
       </c>
     </row>
-    <row r="186" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>3</v>
       </c>
@@ -32629,7 +32629,7 @@
         <v>3.1421984838672872</v>
       </c>
     </row>
-    <row r="187" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>3</v>
       </c>
@@ -32649,7 +32649,7 @@
         <v>3.1429550854444082</v>
       </c>
     </row>
-    <row r="188" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>3</v>
       </c>
@@ -32669,7 +32669,7 @@
         <v>3.1036085686636739</v>
       </c>
     </row>
-    <row r="189" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>3</v>
       </c>
@@ -32689,7 +32689,7 @@
         <v>3.101181171597633</v>
       </c>
     </row>
-    <row r="190" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>3</v>
       </c>
@@ -32709,7 +32709,7 @@
         <v>3.148215963611432</v>
       </c>
     </row>
-    <row r="191" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>3</v>
       </c>
@@ -32729,7 +32729,7 @@
         <v>2.9412569478636281</v>
       </c>
     </row>
-    <row r="192" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>3</v>
       </c>
@@ -32749,7 +32749,7 @@
         <v>3.000599727250068</v>
       </c>
     </row>
-    <row r="193" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>3</v>
       </c>
@@ -32769,7 +32769,7 @@
         <v>2.931646154610021</v>
       </c>
     </row>
-    <row r="194" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>3</v>
       </c>
@@ -32789,7 +32789,7 @@
         <v>2.9278258516357218</v>
       </c>
     </row>
-    <row r="195" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>3</v>
       </c>
@@ -32809,7 +32809,7 @@
         <v>2.9990158070591799</v>
       </c>
     </row>
-    <row r="196" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>3</v>
       </c>
@@ -32829,7 +32829,7 @@
         <v>2.9744652956207802</v>
       </c>
     </row>
-    <row r="197" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>3</v>
       </c>
@@ -32849,7 +32849,7 @@
         <v>2.9998723197123391</v>
       </c>
     </row>
-    <row r="198" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>3</v>
       </c>
@@ -32869,7 +32869,7 @@
         <v>2.858461010560672</v>
       </c>
     </row>
-    <row r="199" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>3</v>
       </c>
@@ -32889,7 +32889,7 @@
         <v>2.917716723415952</v>
       </c>
     </row>
-    <row r="200" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>3</v>
       </c>
@@ -32918,9 +32918,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1AC712-2955-4DDF-90DA-8A6F495FE37F}">
   <dimension ref="A1:AG200"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>0.3</v>
       </c>
@@ -32940,7 +32940,7 @@
         <v>0.2244049146159082</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.3</v>
       </c>
@@ -32960,7 +32960,7 @@
         <v>0.29669438507573043</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.3</v>
       </c>
@@ -32980,7 +32980,7 @@
         <v>0.28413256057660607</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.3</v>
       </c>
@@ -33000,7 +33000,7 @@
         <v>0.24612139195094679</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -33020,7 +33020,7 @@
         <v>0.2586599311173301</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0.3</v>
       </c>
@@ -33040,7 +33040,7 @@
         <v>0.25739169036105197</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.3</v>
       </c>
@@ -33060,7 +33060,7 @@
         <v>0.3259311987765785</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0.3</v>
       </c>
@@ -33080,7 +33080,7 @@
         <v>0.25127335435944959</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.3</v>
       </c>
@@ -33100,7 +33100,7 @@
         <v>0.25498795191662937</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.3</v>
       </c>
@@ -33120,7 +33120,7 @@
         <v>0.2504928486289062</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0.3</v>
       </c>
@@ -33140,7 +33140,7 @@
         <v>0.27233798120524932</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0.3</v>
       </c>
@@ -33160,7 +33160,7 @@
         <v>0.26638614954840678</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0.3</v>
       </c>
@@ -33180,7 +33180,7 @@
         <v>0.27865524653794388</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0.3</v>
       </c>
@@ -33200,7 +33200,7 @@
         <v>0.27484601735917202</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0.3</v>
       </c>
@@ -33220,7 +33220,7 @@
         <v>0.29601674448591719</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0.3</v>
       </c>
@@ -33240,7 +33240,7 @@
         <v>0.28688917498353739</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0.3</v>
       </c>
@@ -33260,7 +33260,7 @@
         <v>0.28232035207707451</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>0.3</v>
       </c>
@@ -33280,7 +33280,7 @@
         <v>0.28607812128998372</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>0.3</v>
       </c>
@@ -33300,7 +33300,7 @@
         <v>0.2884366226230255</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>0.3</v>
       </c>
@@ -33320,7 +33320,7 @@
         <v>0.27538546486789928</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>0.6</v>
       </c>
@@ -33340,7 +33340,7 @@
         <v>0.95675674762438456</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>0.6</v>
       </c>
@@ -33360,7 +33360,7 @@
         <v>0.93691847555243513</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>0.6</v>
       </c>
@@ -33380,7 +33380,7 @@
         <v>0.97521337353393633</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>0.6</v>
       </c>
@@ -33400,7 +33400,7 @@
         <v>0.94768156341425414</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>0.6</v>
       </c>
@@ -33420,7 +33420,7 @@
         <v>0.95091019273221855</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>0.6</v>
       </c>
@@ -33440,7 +33440,7 @@
         <v>0.97970658748589745</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>0.6</v>
       </c>
@@ -33460,7 +33460,7 @@
         <v>0.99544970397905264</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>0.6</v>
       </c>
@@ -33480,7 +33480,7 @@
         <v>0.98276787495959095</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>0.6</v>
       </c>
@@ -33500,7 +33500,7 @@
         <v>0.95254343260411956</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>0.6</v>
       </c>
@@ -33520,7 +33520,7 @@
         <v>0.96927833456950774</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>0.6</v>
       </c>
@@ -33540,7 +33540,7 @@
         <v>0.73116702813917556</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>0.6</v>
       </c>
@@ -33560,7 +33560,7 @@
         <v>0.72145135407916072</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>0.6</v>
       </c>
@@ -33580,7 +33580,7 @@
         <v>0.7577111274251549</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>0.6</v>
       </c>
@@ -33600,7 +33600,7 @@
         <v>0.76029441941842268</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>0.6</v>
       </c>
@@ -33620,7 +33620,7 @@
         <v>0.74976578863831822</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>0.6</v>
       </c>
@@ -33640,7 +33640,7 @@
         <v>0.76300170456066407</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>0.6</v>
       </c>
@@ -33660,7 +33660,7 @@
         <v>0.77301965846287457</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>0.6</v>
       </c>
@@ -33680,7 +33680,7 @@
         <v>0.82921028337903957</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>0.6</v>
       </c>
@@ -33700,7 +33700,7 @@
         <v>0.74165588279144901</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>0.6</v>
       </c>
@@ -33720,7 +33720,7 @@
         <v>0.8277760975738393</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>0.9</v>
       </c>
@@ -33740,7 +33740,7 @@
         <v>1.113178433379558</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>0.9</v>
       </c>
@@ -33760,7 +33760,7 @@
         <v>1.1198148768278819</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>0.9</v>
       </c>
@@ -33780,7 +33780,7 @@
         <v>1.13244169552259</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>0.9</v>
       </c>
@@ -33800,7 +33800,7 @@
         <v>1.1246384941084939</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>0.9</v>
       </c>
@@ -33820,7 +33820,7 @@
         <v>1.13606758556665</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>0.9</v>
       </c>
@@ -33840,7 +33840,7 @@
         <v>1.0895125865856381</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>0.9</v>
       </c>
@@ -33860,7 +33860,7 @@
         <v>1.143385092072646</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>0.9</v>
       </c>
@@ -33880,7 +33880,7 @@
         <v>1.081033258374178</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>0.9</v>
       </c>
@@ -33900,7 +33900,7 @@
         <v>1.0879318942317431</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>0.9</v>
       </c>
@@ -33920,7 +33920,7 @@
         <v>1.0784091434998779</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>0.9</v>
       </c>
@@ -33940,7 +33940,7 @@
         <v>0.84764933001294818</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>0.9</v>
       </c>
@@ -33960,7 +33960,7 @@
         <v>0.88095753961466405</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>0.9</v>
       </c>
@@ -33980,7 +33980,7 @@
         <v>0.84557154551207514</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>0.9</v>
       </c>
@@ -34000,7 +34000,7 @@
         <v>0.79447033630044839</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>0.9</v>
       </c>
@@ -34020,7 +34020,7 @@
         <v>0.83902576621301339</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>0.9</v>
       </c>
@@ -34040,7 +34040,7 @@
         <v>0.86280892572662715</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>0.9</v>
       </c>
@@ -34060,7 +34060,7 @@
         <v>0.77109106761103563</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>0.9</v>
       </c>
@@ -34080,7 +34080,7 @@
         <v>0.84213553014137998</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>0.9</v>
       </c>
@@ -34100,7 +34100,7 @@
         <v>0.84656643125616382</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>0.9</v>
       </c>
@@ -34120,7 +34120,7 @@
         <v>0.88216828044502948</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1.2</v>
       </c>
@@ -34140,7 +34140,7 @@
         <v>1.3252148530927059</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1.2</v>
       </c>
@@ -34160,7 +34160,7 @@
         <v>1.229746492657904</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1.2</v>
       </c>
@@ -34180,7 +34180,7 @@
         <v>1.296492368661867</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1.2</v>
       </c>
@@ -34200,7 +34200,7 @@
         <v>1.2852243976402979</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1.2</v>
       </c>
@@ -34220,7 +34220,7 @@
         <v>1.29569701553315</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1.2</v>
       </c>
@@ -34240,7 +34240,7 @@
         <v>1.3044573321211139</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1.2</v>
       </c>
@@ -34260,7 +34260,7 @@
         <v>1.316381043502975</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>1.2</v>
       </c>
@@ -34280,7 +34280,7 @@
         <v>1.261809784173537</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>1.2</v>
       </c>
@@ -34300,7 +34300,7 @@
         <v>1.3157088987498551</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>1.2</v>
       </c>
@@ -34320,7 +34320,7 @@
         <v>1.286543615954848</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>1.2</v>
       </c>
@@ -34340,7 +34340,7 @@
         <v>1.3963854836950009</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1.2</v>
       </c>
@@ -34360,7 +34360,7 @@
         <v>1.3586878727288429</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>1.2</v>
       </c>
@@ -34380,7 +34380,7 @@
         <v>1.3899101983654949</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1.2</v>
       </c>
@@ -34400,7 +34400,7 @@
         <v>1.3957220895575111</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1.2</v>
       </c>
@@ -34420,7 +34420,7 @@
         <v>1.4043846437875509</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1.2</v>
       </c>
@@ -34440,7 +34440,7 @@
         <v>1.382893017324087</v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1.2</v>
       </c>
@@ -34460,7 +34460,7 @@
         <v>1.387109730679059</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1.2</v>
       </c>
@@ -34480,7 +34480,7 @@
         <v>1.378225959106202</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>1.2</v>
       </c>
@@ -34500,7 +34500,7 @@
         <v>1.4050547075221489</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>1.2</v>
       </c>
@@ -34520,7 +34520,7 @@
         <v>1.382692762728911</v>
       </c>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>1.5</v>
       </c>
@@ -34540,7 +34540,7 @@
         <v>1.519949567282465</v>
       </c>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>1.5</v>
       </c>
@@ -34560,7 +34560,7 @@
         <v>1.5339259074955309</v>
       </c>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1.5</v>
       </c>
@@ -34580,7 +34580,7 @@
         <v>1.5146564919322221</v>
       </c>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1.5</v>
       </c>
@@ -34600,7 +34600,7 @@
         <v>1.477481983750496</v>
       </c>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1.5</v>
       </c>
@@ -34620,7 +34620,7 @@
         <v>1.4595095041858019</v>
       </c>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1.5</v>
       </c>
@@ -34640,7 +34640,7 @@
         <v>1.5045344494537061</v>
       </c>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1.5</v>
       </c>
@@ -34660,7 +34660,7 @@
         <v>1.4759142300320649</v>
       </c>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1.5</v>
       </c>
@@ -34680,7 +34680,7 @@
         <v>1.47569973841794</v>
       </c>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1.5</v>
       </c>
@@ -34700,7 +34700,7 @@
         <v>1.492951699001821</v>
       </c>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1.5</v>
       </c>
@@ -34720,7 +34720,7 @@
         <v>1.5117223852800239</v>
       </c>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>1.5</v>
       </c>
@@ -34740,7 +34740,7 @@
         <v>1.458013303765713</v>
       </c>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1.5</v>
       </c>
@@ -34760,7 +34760,7 @@
         <v>1.4565314835726619</v>
       </c>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1.5</v>
       </c>
@@ -34780,7 +34780,7 @@
         <v>1.439353102966979</v>
       </c>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1.5</v>
       </c>
@@ -34800,7 +34800,7 @@
         <v>1.4601977915330251</v>
       </c>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1.5</v>
       </c>
@@ -34820,7 +34820,7 @@
         <v>1.435856058132061</v>
       </c>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1.5</v>
       </c>
@@ -34840,7 +34840,7 @@
         <v>1.448038975866202</v>
       </c>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>1.5</v>
       </c>
@@ -34860,7 +34860,7 @@
         <v>1.3916813844798981</v>
       </c>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1.5</v>
       </c>
@@ -34880,7 +34880,7 @@
         <v>1.4054871610027251</v>
       </c>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1.5</v>
       </c>
@@ -34900,7 +34900,7 @@
         <v>1.408415131242398</v>
       </c>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>1.5</v>
       </c>
@@ -34920,7 +34920,7 @@
         <v>1.472233491256338</v>
       </c>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1.8</v>
       </c>
@@ -34940,7 +34940,7 @@
         <v>1.789987751768453</v>
       </c>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1.8</v>
       </c>
@@ -34960,7 +34960,7 @@
         <v>1.8100717831125841</v>
       </c>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1.8</v>
       </c>
@@ -34980,7 +34980,7 @@
         <v>1.786412341800955</v>
       </c>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1.8</v>
       </c>
@@ -35000,7 +35000,7 @@
         <v>1.792416123068133</v>
       </c>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1.8</v>
       </c>
@@ -35020,7 +35020,7 @@
         <v>1.7735719003598289</v>
       </c>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>1.8</v>
       </c>
@@ -35040,7 +35040,7 @@
         <v>1.7912329656152639</v>
       </c>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>1.8</v>
       </c>
@@ -35060,7 +35060,7 @@
         <v>1.7945077871912749</v>
       </c>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>1.8</v>
       </c>
@@ -35080,7 +35080,7 @@
         <v>1.761265770277382</v>
       </c>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>1.8</v>
       </c>
@@ -35100,7 +35100,7 @@
         <v>1.8057505512903811</v>
       </c>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1.8</v>
       </c>
@@ -35120,7 +35120,7 @@
         <v>1.7636109865787271</v>
       </c>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>1.8</v>
       </c>
@@ -35140,7 +35140,7 @@
         <v>1.745122541263489</v>
       </c>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1.8</v>
       </c>
@@ -35160,7 +35160,7 @@
         <v>1.7011201874256181</v>
       </c>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>1.8</v>
       </c>
@@ -35180,7 +35180,7 @@
         <v>1.7647963992554301</v>
       </c>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1.8</v>
       </c>
@@ -35200,7 +35200,7 @@
         <v>1.7596807729390971</v>
       </c>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>1.8</v>
       </c>
@@ -35220,7 +35220,7 @@
         <v>1.727797061625429</v>
       </c>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>1.8</v>
       </c>
@@ -35240,7 +35240,7 @@
         <v>1.7384376493500051</v>
       </c>
     </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1.8</v>
       </c>
@@ -35260,7 +35260,7 @@
         <v>1.787377855506646</v>
       </c>
     </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>1.8</v>
       </c>
@@ -35280,7 +35280,7 @@
         <v>1.7813225144074569</v>
       </c>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1.8</v>
       </c>
@@ -35300,7 +35300,7 @@
         <v>1.770915057159294</v>
       </c>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>1.8</v>
       </c>
@@ -35320,7 +35320,7 @@
         <v>1.730810955214038</v>
       </c>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2.1</v>
       </c>
@@ -35340,7 +35340,7 @@
         <v>2.1822834978690659</v>
       </c>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2.1</v>
       </c>
@@ -35360,7 +35360,7 @@
         <v>2.152191100068503</v>
       </c>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2.1</v>
       </c>
@@ -35380,7 +35380,7 @@
         <v>2.1322791550049698</v>
       </c>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2.1</v>
       </c>
@@ -35400,7 +35400,7 @@
         <v>2.230432567590134</v>
       </c>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2.1</v>
       </c>
@@ -35420,7 +35420,7 @@
         <v>2.1519701865507201</v>
       </c>
     </row>
-    <row r="126" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2.1</v>
       </c>
@@ -35440,7 +35440,7 @@
         <v>2.1654623147985972</v>
       </c>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2.1</v>
       </c>
@@ -35460,7 +35460,7 @@
         <v>2.1726500166383498</v>
       </c>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2.1</v>
       </c>
@@ -35480,7 +35480,7 @@
         <v>2.188346629073576</v>
       </c>
     </row>
-    <row r="129" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2.1</v>
       </c>
@@ -35500,7 +35500,7 @@
         <v>2.159575778074359</v>
       </c>
     </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2.1</v>
       </c>
@@ -35520,7 +35520,7 @@
         <v>2.124859566878031</v>
       </c>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2.1</v>
       </c>
@@ -35540,7 +35540,7 @@
         <v>2.186966669248755</v>
       </c>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2.1</v>
       </c>
@@ -35560,7 +35560,7 @@
         <v>2.149959399068643</v>
       </c>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2.1</v>
       </c>
@@ -35580,7 +35580,7 @@
         <v>2.1859212017949412</v>
       </c>
     </row>
-    <row r="134" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2.1</v>
       </c>
@@ -35600,7 +35600,7 @@
         <v>2.2020643641916808</v>
       </c>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2.1</v>
       </c>
@@ -35620,7 +35620,7 @@
         <v>2.2223185040625508</v>
       </c>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2.1</v>
       </c>
@@ -35640,7 +35640,7 @@
         <v>2.1759880652028221</v>
       </c>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2.1</v>
       </c>
@@ -35660,7 +35660,7 @@
         <v>2.2320314835515211</v>
       </c>
     </row>
-    <row r="138" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2.1</v>
       </c>
@@ -35680,7 +35680,7 @@
         <v>2.2077515212015051</v>
       </c>
     </row>
-    <row r="139" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2.1</v>
       </c>
@@ -35700,7 +35700,7 @@
         <v>2.1915099800196631</v>
       </c>
     </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2.1</v>
       </c>
@@ -35720,7 +35720,7 @@
         <v>2.2082896523763722</v>
       </c>
     </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2.4</v>
       </c>
@@ -35740,7 +35740,7 @@
         <v>2.4956080694645149</v>
       </c>
     </row>
-    <row r="142" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2.4</v>
       </c>
@@ -35760,7 +35760,7 @@
         <v>2.4881502654009111</v>
       </c>
     </row>
-    <row r="143" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2.4</v>
       </c>
@@ -35780,7 +35780,7 @@
         <v>2.392471600915024</v>
       </c>
     </row>
-    <row r="144" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2.4</v>
       </c>
@@ -35800,7 +35800,7 @@
         <v>2.429636866858722</v>
       </c>
     </row>
-    <row r="145" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2.4</v>
       </c>
@@ -35820,7 +35820,7 @@
         <v>2.4950921367686791</v>
       </c>
     </row>
-    <row r="146" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2.4</v>
       </c>
@@ -35840,7 +35840,7 @@
         <v>2.42386965420302</v>
       </c>
     </row>
-    <row r="147" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2.4</v>
       </c>
@@ -35860,7 +35860,7 @@
         <v>2.417491244506504</v>
       </c>
     </row>
-    <row r="148" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2.4</v>
       </c>
@@ -35880,7 +35880,7 @@
         <v>2.3914368821712029</v>
       </c>
     </row>
-    <row r="149" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2.4</v>
       </c>
@@ -35900,7 +35900,7 @@
         <v>2.4280422546391698</v>
       </c>
     </row>
-    <row r="150" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2.4</v>
       </c>
@@ -35920,7 +35920,7 @@
         <v>2.4507671119743399</v>
       </c>
     </row>
-    <row r="151" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2.4</v>
       </c>
@@ -35940,7 +35940,7 @@
         <v>2.475413101410838</v>
       </c>
     </row>
-    <row r="152" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2.4</v>
       </c>
@@ -35960,7 +35960,7 @@
         <v>2.4415002592407959</v>
       </c>
     </row>
-    <row r="153" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2.4</v>
       </c>
@@ -35980,7 +35980,7 @@
         <v>2.445853077738017</v>
       </c>
     </row>
-    <row r="154" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2.4</v>
       </c>
@@ -36000,7 +36000,7 @@
         <v>2.492797531534229</v>
       </c>
     </row>
-    <row r="155" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2.4</v>
       </c>
@@ -36020,7 +36020,7 @@
         <v>2.49433976234767</v>
       </c>
     </row>
-    <row r="156" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2.4</v>
       </c>
@@ -36040,7 +36040,7 @@
         <v>2.4824875060465912</v>
       </c>
     </row>
-    <row r="157" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2.4</v>
       </c>
@@ -36060,7 +36060,7 @@
         <v>2.4196615260337682</v>
       </c>
     </row>
-    <row r="158" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2.4</v>
       </c>
@@ -36080,7 +36080,7 @@
         <v>2.4008229511921719</v>
       </c>
     </row>
-    <row r="159" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2.4</v>
       </c>
@@ -36100,7 +36100,7 @@
         <v>2.47218434231202</v>
       </c>
     </row>
-    <row r="160" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2.4</v>
       </c>
@@ -36120,7 +36120,7 @@
         <v>2.4807722585747372</v>
       </c>
     </row>
-    <row r="161" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2.7</v>
       </c>
@@ -36140,7 +36140,7 @@
         <v>2.7780012884164238</v>
       </c>
     </row>
-    <row r="162" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2.7</v>
       </c>
@@ -36160,7 +36160,7 @@
         <v>2.7266616324446811</v>
       </c>
     </row>
-    <row r="163" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2.7</v>
       </c>
@@ -36180,7 +36180,7 @@
         <v>2.7102950352904291</v>
       </c>
     </row>
-    <row r="164" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2.7</v>
       </c>
@@ -36200,7 +36200,7 @@
         <v>2.7971544274194389</v>
       </c>
     </row>
-    <row r="165" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2.7</v>
       </c>
@@ -36220,7 +36220,7 @@
         <v>2.7087537040295722</v>
       </c>
     </row>
-    <row r="166" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2.7</v>
       </c>
@@ -36240,7 +36240,7 @@
         <v>2.7284370835048048</v>
       </c>
     </row>
-    <row r="167" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2.7</v>
       </c>
@@ -36260,7 +36260,7 @@
         <v>2.7233119472940932</v>
       </c>
     </row>
-    <row r="168" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2.7</v>
       </c>
@@ -36280,7 +36280,7 @@
         <v>2.7313915766595258</v>
       </c>
     </row>
-    <row r="169" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2.7</v>
       </c>
@@ -36300,7 +36300,7 @@
         <v>2.6708229346030961</v>
       </c>
     </row>
-    <row r="170" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2.7</v>
       </c>
@@ -36320,7 +36320,7 @@
         <v>2.7020814408683909</v>
       </c>
     </row>
-    <row r="171" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2.7</v>
       </c>
@@ -36340,7 +36340,7 @@
         <v>2.679951566146721</v>
       </c>
     </row>
-    <row r="172" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2.7</v>
       </c>
@@ -36360,7 +36360,7 @@
         <v>2.67400840263993</v>
       </c>
     </row>
-    <row r="173" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2.7</v>
       </c>
@@ -36380,7 +36380,7 @@
         <v>2.6782218131948872</v>
       </c>
     </row>
-    <row r="174" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2.7</v>
       </c>
@@ -36400,7 +36400,7 @@
         <v>2.628082034112277</v>
       </c>
     </row>
-    <row r="175" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2.7</v>
       </c>
@@ -36420,7 +36420,7 @@
         <v>2.6804868265160349</v>
       </c>
     </row>
-    <row r="176" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2.7</v>
       </c>
@@ -36440,7 +36440,7 @@
         <v>2.664167902408749</v>
       </c>
     </row>
-    <row r="177" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2.7</v>
       </c>
@@ -36460,7 +36460,7 @@
         <v>2.69502791385211</v>
       </c>
     </row>
-    <row r="178" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2.7</v>
       </c>
@@ -36480,7 +36480,7 @@
         <v>2.6826956028096731</v>
       </c>
     </row>
-    <row r="179" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2.7</v>
       </c>
@@ -36500,7 +36500,7 @@
         <v>2.674712066240287</v>
       </c>
     </row>
-    <row r="180" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2.7</v>
       </c>
@@ -36520,7 +36520,7 @@
         <v>2.7169556229075491</v>
       </c>
     </row>
-    <row r="181" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>3</v>
       </c>
@@ -36540,7 +36540,7 @@
         <v>2.977922405351118</v>
       </c>
     </row>
-    <row r="182" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>3</v>
       </c>
@@ -36560,7 +36560,7 @@
         <v>2.923401334647342</v>
       </c>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>3</v>
       </c>
@@ -36580,7 +36580,7 @@
         <v>2.8813134437096681</v>
       </c>
     </row>
-    <row r="184" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>3</v>
       </c>
@@ -36600,7 +36600,7 @@
         <v>2.899620093107433</v>
       </c>
     </row>
-    <row r="185" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>3</v>
       </c>
@@ -36620,7 +36620,7 @@
         <v>2.937723117751033</v>
       </c>
     </row>
-    <row r="186" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>3</v>
       </c>
@@ -36640,7 +36640,7 @@
         <v>2.9471788548760012</v>
       </c>
     </row>
-    <row r="187" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>3</v>
       </c>
@@ -36660,7 +36660,7 @@
         <v>2.9507920420353102</v>
       </c>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>3</v>
       </c>
@@ -36680,7 +36680,7 @@
         <v>2.9436137688767281</v>
       </c>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>3</v>
       </c>
@@ -36700,7 +36700,7 @@
         <v>2.8872384508840399</v>
       </c>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>3</v>
       </c>
@@ -36720,7 +36720,7 @@
         <v>2.9672150999202991</v>
       </c>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>3</v>
       </c>
@@ -36740,7 +36740,7 @@
         <v>2.8670425040838889</v>
       </c>
     </row>
-    <row r="192" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>3</v>
       </c>
@@ -36760,7 +36760,7 @@
         <v>2.814612233234604</v>
       </c>
     </row>
-    <row r="193" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>3</v>
       </c>
@@ -36780,7 +36780,7 @@
         <v>2.941680635409718</v>
       </c>
     </row>
-    <row r="194" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>3</v>
       </c>
@@ -36800,7 +36800,7 @@
         <v>2.8096036618138922</v>
       </c>
     </row>
-    <row r="195" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>3</v>
       </c>
@@ -36820,7 +36820,7 @@
         <v>2.9384901740496701</v>
       </c>
     </row>
-    <row r="196" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>3</v>
       </c>
@@ -36840,7 +36840,7 @@
         <v>2.921502586994126</v>
       </c>
     </row>
-    <row r="197" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>3</v>
       </c>
@@ -36860,7 +36860,7 @@
         <v>2.918930006743758</v>
       </c>
     </row>
-    <row r="198" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>3</v>
       </c>
@@ -36880,7 +36880,7 @@
         <v>2.7680868527535512</v>
       </c>
     </row>
-    <row r="199" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>3</v>
       </c>
@@ -36900,7 +36900,7 @@
         <v>2.7819960351219661</v>
       </c>
     </row>
-    <row r="200" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>3</v>
       </c>
